--- a/Team-Data/2007-08/4-1-2007-08.xlsx
+++ b/Team-Data/2007-08/4-1-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,10 +818,10 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
@@ -781,7 +848,7 @@
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -793,7 +860,7 @@
         <v>12</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -861,28 +928,28 @@
         <v>36.4</v>
       </c>
       <c r="J3" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.476</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M3" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.379</v>
+        <v>0.376</v>
       </c>
       <c r="O3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P3" t="n">
         <v>26.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10</v>
@@ -912,16 +979,16 @@
         <v>22.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="AC3" t="n">
         <v>10.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -945,7 +1012,7 @@
         <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM3" t="n">
         <v>13</v>
@@ -954,28 +1021,28 @@
         <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
         <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
         <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
         <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>5</v>
@@ -984,7 +1051,7 @@
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
@@ -993,7 +1060,7 @@
         <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1154,13 +1221,13 @@
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1175,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" t="n">
         <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>0.392</v>
+        <v>0.397</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J5" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
         <v>0.431</v>
@@ -1237,13 +1304,13 @@
         <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O5" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q5" t="n">
         <v>0.754</v>
@@ -1252,10 +1319,10 @@
         <v>13.3</v>
       </c>
       <c r="S5" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="U5" t="n">
         <v>21.8</v>
@@ -1264,7 +1331,7 @@
         <v>14.5</v>
       </c>
       <c r="W5" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.2</v>
@@ -1273,19 +1340,19 @@
         <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1297,10 +1364,10 @@
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1318,19 +1385,19 @@
         <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
@@ -1342,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1482,7 +1549,7 @@
         <v>4</v>
       </c>
       <c r="AI6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ6" t="n">
         <v>14</v>
@@ -1491,7 +1558,7 @@
         <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM6" t="n">
         <v>11</v>
@@ -1533,13 +1600,13 @@
         <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
         <v>24</v>
       </c>
       <c r="BB6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
         <v>15</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -1649,22 +1716,22 @@
         <v>4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
@@ -1676,7 +1743,7 @@
         <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="n">
         <v>19</v>
@@ -1694,7 +1761,7 @@
         <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.613</v>
+        <v>0.608</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
@@ -1771,7 +1838,7 @@
         <v>40.1</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K8" t="n">
         <v>0.468</v>
@@ -1783,16 +1850,16 @@
         <v>19.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R8" t="n">
         <v>11.4</v>
@@ -1810,49 +1877,49 @@
         <v>14.6</v>
       </c>
       <c r="W8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y8" t="n">
         <v>4.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>110</v>
+        <v>109.8</v>
       </c>
       <c r="AC8" t="n">
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
         <v>11</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
         <v>13</v>
@@ -1870,13 +1937,13 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
         <v>5</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1894,10 +1961,10 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
         <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>0.716</v>
+        <v>0.712</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1956,25 +2023,25 @@
         <v>79.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N9" t="n">
         <v>0.372</v>
       </c>
       <c r="O9" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P9" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R9" t="n">
         <v>11.7</v>
@@ -1986,13 +2053,13 @@
         <v>41</v>
       </c>
       <c r="U9" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V9" t="n">
         <v>11.6</v>
       </c>
       <c r="W9" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X9" t="n">
         <v>5.6</v>
@@ -2004,7 +2071,7 @@
         <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB9" t="n">
         <v>97.5</v>
@@ -2013,7 +2080,7 @@
         <v>7.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,7 +2095,7 @@
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
         <v>22</v>
@@ -2046,13 +2113,13 @@
         <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP9" t="n">
         <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
         <v>11</v>
@@ -2064,7 +2131,7 @@
         <v>23</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2076,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -2117,34 +2184,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" t="n">
         <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="J10" t="n">
         <v>89.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L10" t="n">
         <v>9.4</v>
       </c>
       <c r="M10" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="N10" t="n">
         <v>0.352</v>
@@ -2156,19 +2223,19 @@
         <v>25.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R10" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S10" t="n">
         <v>30.3</v>
       </c>
       <c r="T10" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U10" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="V10" t="n">
         <v>13.1</v>
@@ -2183,40 +2250,40 @@
         <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.8</v>
+        <v>111.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG10" t="n">
         <v>11</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>2</v>
@@ -2246,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
         <v>5</v>
@@ -2258,10 +2325,10 @@
         <v>19</v>
       </c>
       <c r="AY10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA10" t="n">
         <v>12</v>
@@ -2270,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -2299,64 +2366,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" t="n">
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.662</v>
+        <v>0.671</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J11" t="n">
         <v>81.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.338</v>
+        <v>0.339</v>
       </c>
       <c r="O11" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P11" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.725</v>
+        <v>0.723</v>
       </c>
       <c r="R11" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S11" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T11" t="n">
         <v>44.6</v>
       </c>
       <c r="U11" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V11" t="n">
         <v>13.9</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X11" t="n">
         <v>5.2</v>
@@ -2365,25 +2432,25 @@
         <v>4.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB11" t="n">
         <v>96.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="n">
         <v>7</v>
@@ -2398,10 +2465,10 @@
         <v>12</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
@@ -2410,16 +2477,16 @@
         <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
         <v>6</v>
@@ -2446,7 +2513,7 @@
         <v>3</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
         <v>19</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2577,7 +2644,7 @@
         <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK12" t="n">
         <v>25</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
@@ -2598,7 +2665,7 @@
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2610,10 +2677,10 @@
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2786,16 +2853,16 @@
         <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT13" t="n">
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2935,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2953,13 +3020,13 @@
         <v>5</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
         <v>15</v>
@@ -2989,7 +3056,7 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3135,10 +3202,10 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
@@ -3153,7 +3220,7 @@
         <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU15" t="n">
         <v>29</v>
@@ -3168,13 +3235,13 @@
         <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ15" t="n">
         <v>5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
         <v>11</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
         <v>29</v>
@@ -3311,7 +3378,7 @@
         <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM16" t="n">
         <v>24</v>
@@ -3326,7 +3393,7 @@
         <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3458,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
         <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>0.342</v>
+        <v>0.333</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.446</v>
@@ -3424,25 +3491,25 @@
         <v>0.341</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R17" t="n">
         <v>12.9</v>
       </c>
       <c r="S17" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="T17" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U17" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
         <v>14.5</v>
@@ -3463,10 +3530,10 @@
         <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.3</v>
+        <v>96</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.6</v>
+        <v>-6.7</v>
       </c>
       <c r="AD17" t="n">
         <v>28</v>
@@ -3481,10 +3548,10 @@
         <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
@@ -3493,7 +3560,7 @@
         <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM17" t="n">
         <v>22</v>
@@ -3502,7 +3569,7 @@
         <v>25</v>
       </c>
       <c r="AO17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP17" t="n">
         <v>23</v>
@@ -3517,10 +3584,10 @@
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV17" t="n">
         <v>14</v>
@@ -3529,10 +3596,10 @@
         <v>22</v>
       </c>
       <c r="AX17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY17" t="n">
         <v>21</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>20</v>
       </c>
       <c r="AZ17" t="n">
         <v>20</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E18" t="n">
         <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>0.26</v>
+        <v>0.264</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J18" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
@@ -3603,22 +3670,22 @@
         <v>15.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O18" t="n">
         <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.735</v>
+        <v>0.734</v>
       </c>
       <c r="R18" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
         <v>41.2</v>
@@ -3630,7 +3697,7 @@
         <v>14.8</v>
       </c>
       <c r="W18" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X18" t="n">
         <v>3.8</v>
@@ -3645,7 +3712,7 @@
         <v>17.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC18" t="n">
         <v>-6.5</v>
@@ -3672,7 +3739,7 @@
         <v>9</v>
       </c>
       <c r="AK18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL18" t="n">
         <v>25</v>
@@ -3717,7 +3784,7 @@
         <v>28</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -3755,22 +3822,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
         <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>0.413</v>
+        <v>0.419</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J19" t="n">
         <v>78.7</v>
@@ -3782,16 +3849,16 @@
         <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N19" t="n">
         <v>0.349</v>
       </c>
       <c r="O19" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="P19" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="Q19" t="n">
         <v>0.731</v>
@@ -3800,7 +3867,7 @@
         <v>11.4</v>
       </c>
       <c r="S19" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T19" t="n">
         <v>42.4</v>
@@ -3812,16 +3879,16 @@
         <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y19" t="n">
         <v>4.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA19" t="n">
         <v>22.5</v>
@@ -3833,19 +3900,19 @@
         <v>-4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>28</v>
@@ -3857,25 +3924,25 @@
         <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM19" t="n">
         <v>18</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
         <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
         <v>13</v>
@@ -3902,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.699</v>
+        <v>0.694</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3958,7 +4025,7 @@
         <v>82.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L20" t="n">
         <v>7.8</v>
@@ -3970,22 +4037,22 @@
         <v>0.393</v>
       </c>
       <c r="O20" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P20" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="Q20" t="n">
         <v>0.77</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.6</v>
@@ -4006,13 +4073,13 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB20" t="n">
         <v>100.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD20" t="n">
         <v>28</v>
@@ -4057,13 +4124,13 @@
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS20" t="n">
         <v>15</v>
       </c>
       <c r="AT20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU20" t="n">
         <v>13</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC20" t="n">
         <v>6</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>0.27</v>
+        <v>0.274</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
       <c r="J21" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L21" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M21" t="n">
         <v>17.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O21" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P21" t="n">
         <v>25.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R21" t="n">
         <v>12.3</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U21" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="V21" t="n">
         <v>14.5</v>
@@ -4191,13 +4258,13 @@
         <v>20.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>-6.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4224,7 +4291,7 @@
         <v>21</v>
       </c>
       <c r="AM21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN21" t="n">
         <v>28</v>
@@ -4239,7 +4306,7 @@
         <v>27</v>
       </c>
       <c r="AR21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
@@ -4251,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
         <v>26</v>
@@ -4269,7 +4336,7 @@
         <v>19</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
         <v>47</v>
       </c>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22" t="n">
-        <v>0.627</v>
+        <v>0.635</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4325,31 +4392,31 @@
         <v>0.473</v>
       </c>
       <c r="L22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M22" t="n">
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>0.387</v>
+        <v>0.386</v>
       </c>
       <c r="O22" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="P22" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R22" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U22" t="n">
         <v>20.4</v>
@@ -4367,19 +4434,19 @@
         <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.4</v>
+        <v>104.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>9</v>
@@ -4391,13 +4458,13 @@
         <v>9</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
         <v>12</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4412,7 +4479,7 @@
         <v>4</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
         <v>3</v>
@@ -4424,10 +4491,10 @@
         <v>28</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
         <v>22</v>
@@ -4439,16 +4506,16 @@
         <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY22" t="n">
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4550,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F23" t="n">
         <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>0.507</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
         <v>81</v>
@@ -4513,16 +4580,16 @@
         <v>11.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="O23" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P23" t="n">
         <v>26.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.707</v>
+        <v>0.705</v>
       </c>
       <c r="R23" t="n">
         <v>13.2</v>
@@ -4531,10 +4598,10 @@
         <v>28.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
         <v>14.6</v>
@@ -4555,16 +4622,16 @@
         <v>21.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4582,7 +4649,7 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4612,10 +4679,10 @@
         <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>4</v>
@@ -4624,16 +4691,16 @@
         <v>9</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
         <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24" t="n">
         <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>0.667</v>
+        <v>0.676</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="J24" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>0.499</v>
       </c>
       <c r="L24" t="n">
         <v>8.6</v>
@@ -4698,13 +4765,13 @@
         <v>0.392</v>
       </c>
       <c r="O24" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P24" t="n">
         <v>24</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.783</v>
+        <v>0.786</v>
       </c>
       <c r="R24" t="n">
         <v>8.699999999999999</v>
@@ -4716,13 +4783,13 @@
         <v>41.1</v>
       </c>
       <c r="U24" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="V24" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W24" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X24" t="n">
         <v>6.5</v>
@@ -4731,34 +4798,34 @@
         <v>3.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>110.3</v>
+        <v>110.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF24" t="n">
         <v>5</v>
       </c>
-      <c r="AF24" t="n">
-        <v>6</v>
-      </c>
       <c r="AG24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
         <v>7</v>
@@ -4776,7 +4843,7 @@
         <v>3</v>
       </c>
       <c r="AO24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP24" t="n">
         <v>21</v>
@@ -4806,13 +4873,13 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ24" t="n">
         <v>9</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4985,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F26" t="n">
         <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>0.459</v>
+        <v>0.452</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,10 +5114,10 @@
         <v>36.9</v>
       </c>
       <c r="J26" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
         <v>6.3</v>
@@ -5062,22 +5129,22 @@
         <v>0.371</v>
       </c>
       <c r="O26" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="P26" t="n">
         <v>27.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="R26" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T26" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="U26" t="n">
         <v>19.1</v>
@@ -5092,7 +5159,7 @@
         <v>4.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z26" t="n">
         <v>22.4</v>
@@ -5104,19 +5171,19 @@
         <v>102.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>6</v>
@@ -5143,7 +5210,7 @@
         <v>2</v>
       </c>
       <c r="AP26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
@@ -5164,7 +5231,7 @@
         <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
         <v>24</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F27" t="n">
         <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J27" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L27" t="n">
         <v>7.5</v>
@@ -5241,25 +5308,25 @@
         <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>0.375</v>
+        <v>0.373</v>
       </c>
       <c r="O27" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="P27" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R27" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T27" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="U27" t="n">
         <v>21.1</v>
@@ -5280,16 +5347,16 @@
         <v>18.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -5301,13 +5368,13 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK27" t="n">
         <v>14</v>
@@ -5319,7 +5386,7 @@
         <v>8</v>
       </c>
       <c r="AN27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO27" t="n">
         <v>26</v>
@@ -5328,16 +5395,16 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
         <v>25</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
         <v>17</v>
@@ -5349,7 +5416,7 @@
         <v>23</v>
       </c>
       <c r="AX27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>11</v>
@@ -5361,7 +5428,7 @@
         <v>23</v>
       </c>
       <c r="BB27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC27" t="n">
         <v>5</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5483,7 +5550,7 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5504,7 +5571,7 @@
         <v>26</v>
       </c>
       <c r="AO28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP28" t="n">
         <v>24</v>
@@ -5516,7 +5583,7 @@
         <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
         <v>3</v>
@@ -5531,7 +5598,7 @@
         <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
@@ -5540,7 +5607,7 @@
         <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
         <v>15</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5674,10 +5741,10 @@
         <v>11</v>
       </c>
       <c r="AK29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5686,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP29" t="n">
         <v>30</v>
@@ -5719,7 +5786,7 @@
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
@@ -5728,7 +5795,7 @@
         <v>12</v>
       </c>
       <c r="BC29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5932,7 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5877,7 +5944,7 @@
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS30" t="n">
         <v>27</v>
@@ -5904,7 +5971,7 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6032,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
         <v>15</v>
@@ -6065,7 +6132,7 @@
         <v>26</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6074,7 +6141,7 @@
         <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-1-2007-08</t>
+          <t>2008-04-01</t>
         </is>
       </c>
     </row>
